--- a/3_Component_Results/PRIVCON/Data/naive_err/AVERAGE_1_9_qoq_errors_first_eval.xlsx
+++ b/3_Component_Results/PRIVCON/Data/naive_err/AVERAGE_1_9_qoq_errors_first_eval.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>Q0</t>
   </si>
@@ -200,6 +200,9 @@
   </si>
   <si>
     <t>2025-07-01 00:00:00_diff</t>
+  </si>
+  <si>
+    <t>2025-10-01 00:00:00_diff</t>
   </si>
 </sst>
 </file>
@@ -557,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1801,6 +1804,9 @@
       <c r="I45">
         <v>-0.007373021042980099</v>
       </c>
+      <c r="J45">
+        <v>0.3025010101917047</v>
+      </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="1" t="s">
@@ -1827,6 +1833,9 @@
       <c r="H46">
         <v>-0.3204039861736021</v>
       </c>
+      <c r="I46">
+        <v>-0.01052995493891729</v>
+      </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="1" t="s">
@@ -1850,6 +1859,9 @@
       <c r="G47">
         <v>0.1820111276841772</v>
       </c>
+      <c r="H47">
+        <v>0.491885158918862</v>
+      </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="1" t="s">
@@ -1870,8 +1882,11 @@
       <c r="F48">
         <v>-0.4696221197246473</v>
       </c>
-    </row>
-    <row r="49" spans="1:5">
+      <c r="G48">
+        <v>-0.1597480884899625</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49" s="1" t="s">
         <v>57</v>
       </c>
@@ -1887,8 +1902,11 @@
       <c r="E49">
         <v>-0.2767225006826664</v>
       </c>
-    </row>
-    <row r="50" spans="1:5">
+      <c r="F49">
+        <v>0.0331515305520185</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50" s="1" t="s">
         <v>58</v>
       </c>
@@ -1901,8 +1919,11 @@
       <c r="D50">
         <v>0.2340189479022286</v>
       </c>
-    </row>
-    <row r="51" spans="1:5">
+      <c r="E50">
+        <v>0.5438929791369134</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51" s="1" t="s">
         <v>59</v>
       </c>
@@ -1912,18 +1933,32 @@
       <c r="C51">
         <v>0.0286182153050305</v>
       </c>
-    </row>
-    <row r="52" spans="1:5">
+      <c r="D51">
+        <v>0.3384922465397153</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B52">
         <v>0.4351041572683414</v>
       </c>
-    </row>
-    <row r="53" spans="1:5">
+      <c r="C52">
+        <v>0.7449781885030262</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53" s="1" t="s">
         <v>61</v>
+      </c>
+      <c r="B53">
+        <v>0.3098740312346848</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
